--- a/x13dico.xlsx
+++ b/x13dico.xlsx
@@ -1,13 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YWYD5I\Documents\00_RJD3_Developpement\RJD3_development\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F04738-2D2D-47F0-B625-DDA173AE464A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" r:id="rId3" sheetId="1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -3017,13 +3030,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3033,7 +3045,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -3051,16 +3063,343 @@
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G335"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1"/>
+    <row r="1" spans="1:7">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -3080,7 +3419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -3103,7 +3442,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -3126,7 +3465,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -3149,7 +3488,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3172,7 +3511,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3195,7 +3534,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -3218,7 +3557,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -3241,7 +3580,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -3264,7 +3603,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -3287,7 +3626,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -3310,7 +3649,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -3333,7 +3672,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -3356,7 +3695,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -3379,7 +3718,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -3402,7 +3741,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -3425,7 +3764,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -3448,7 +3787,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -3471,7 +3810,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -3494,7 +3833,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -3517,7 +3856,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -3540,7 +3879,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -3563,7 +3902,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -3586,7 +3925,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -3609,7 +3948,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -3632,7 +3971,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -3655,7 +3994,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -3678,7 +4017,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -3701,7 +4040,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -3724,7 +4063,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -3747,7 +4086,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -3770,7 +4109,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -3793,7 +4132,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -3816,7 +4155,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -3839,7 +4178,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -3862,7 +4201,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -3885,7 +4224,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -3908,7 +4247,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -3931,7 +4270,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -3954,7 +4293,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -3977,7 +4316,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -4000,7 +4339,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -4023,7 +4362,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -4046,7 +4385,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -4069,7 +4408,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -4092,7 +4431,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -4115,7 +4454,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -4138,7 +4477,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -4161,7 +4500,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -4184,7 +4523,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>54</v>
       </c>
@@ -4207,7 +4546,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>55</v>
       </c>
@@ -4230,7 +4569,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>56</v>
       </c>
@@ -4253,7 +4592,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>57</v>
       </c>
@@ -4276,7 +4615,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>58</v>
       </c>
@@ -4299,7 +4638,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -4322,7 +4661,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>60</v>
       </c>
@@ -4345,7 +4684,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>61</v>
       </c>
@@ -4368,7 +4707,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>62</v>
       </c>
@@ -4391,7 +4730,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>63</v>
       </c>
@@ -4414,7 +4753,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -4437,7 +4776,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>65</v>
       </c>
@@ -4460,7 +4799,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -4483,7 +4822,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>67</v>
       </c>
@@ -4506,7 +4845,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>68</v>
       </c>
@@ -4529,7 +4868,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>69</v>
       </c>
@@ -4552,7 +4891,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
         <v>70</v>
       </c>
@@ -4575,7 +4914,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
         <v>71</v>
       </c>
@@ -4598,7 +4937,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
         <v>72</v>
       </c>
@@ -4621,7 +4960,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
         <v>73</v>
       </c>
@@ -4644,7 +4983,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
         <v>74</v>
       </c>
@@ -4667,7 +5006,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
         <v>75</v>
       </c>
@@ -4690,7 +5029,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
         <v>76</v>
       </c>
@@ -4713,7 +5052,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
         <v>77</v>
       </c>
@@ -4736,7 +5075,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
         <v>78</v>
       </c>
@@ -4759,7 +5098,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
         <v>79</v>
       </c>
@@ -4782,7 +5121,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>80</v>
       </c>
@@ -4805,7 +5144,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>81</v>
       </c>
@@ -4828,7 +5167,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>82</v>
       </c>
@@ -4851,7 +5190,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -4874,7 +5213,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
         <v>84</v>
       </c>
@@ -4897,7 +5236,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
         <v>85</v>
       </c>
@@ -4920,7 +5259,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
         <v>86</v>
       </c>
@@ -4943,7 +5282,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:7">
       <c r="A83" t="s">
         <v>87</v>
       </c>
@@ -4966,7 +5305,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
         <v>88</v>
       </c>
@@ -4989,7 +5328,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
         <v>89</v>
       </c>
@@ -5012,7 +5351,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
         <v>90</v>
       </c>
@@ -5035,7 +5374,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
         <v>91</v>
       </c>
@@ -5058,7 +5397,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:7">
       <c r="A88" t="s">
         <v>92</v>
       </c>
@@ -5081,7 +5420,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:7">
       <c r="A89" t="s">
         <v>93</v>
       </c>
@@ -5104,7 +5443,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:7">
       <c r="A90" t="s">
         <v>94</v>
       </c>
@@ -5127,7 +5466,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:7">
       <c r="A91" t="s">
         <v>95</v>
       </c>
@@ -5150,7 +5489,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:7">
       <c r="A92" t="s">
         <v>96</v>
       </c>
@@ -5173,7 +5512,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:7">
       <c r="A93" t="s">
         <v>97</v>
       </c>
@@ -5196,7 +5535,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:7">
       <c r="A94" t="s">
         <v>98</v>
       </c>
@@ -5219,7 +5558,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:7">
       <c r="A95" t="s">
         <v>99</v>
       </c>
@@ -5242,7 +5581,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:7">
       <c r="A96" t="s">
         <v>100</v>
       </c>
@@ -5265,7 +5604,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
         <v>101</v>
       </c>
@@ -5288,7 +5627,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:7">
       <c r="A98" t="s">
         <v>102</v>
       </c>
@@ -5311,7 +5650,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:7">
       <c r="A99" t="s">
         <v>103</v>
       </c>
@@ -5334,7 +5673,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:7">
       <c r="A100" t="s">
         <v>104</v>
       </c>
@@ -5357,7 +5696,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:7">
       <c r="A101" t="s">
         <v>105</v>
       </c>
@@ -5380,7 +5719,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:7">
       <c r="A102" t="s">
         <v>106</v>
       </c>
@@ -5403,7 +5742,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:7">
       <c r="A103" t="s">
         <v>107</v>
       </c>
@@ -5426,7 +5765,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:7">
       <c r="A104" t="s">
         <v>108</v>
       </c>
@@ -5449,7 +5788,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:7">
       <c r="A105" t="s">
         <v>109</v>
       </c>
@@ -5472,7 +5811,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:7">
       <c r="A106" t="s">
         <v>110</v>
       </c>
@@ -5495,7 +5834,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:7">
       <c r="A107" t="s">
         <v>111</v>
       </c>
@@ -5518,7 +5857,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:7">
       <c r="A108" t="s">
         <v>112</v>
       </c>
@@ -5541,7 +5880,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:7">
       <c r="A109" t="s">
         <v>113</v>
       </c>
@@ -5564,7 +5903,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:7">
       <c r="A110" t="s">
         <v>114</v>
       </c>
@@ -5587,7 +5926,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:7">
       <c r="A111" t="s">
         <v>115</v>
       </c>
@@ -5610,7 +5949,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:7">
       <c r="A112" t="s">
         <v>116</v>
       </c>
@@ -5633,7 +5972,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:7">
       <c r="A113" t="s">
         <v>117</v>
       </c>
@@ -5656,7 +5995,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
         <v>118</v>
       </c>
@@ -5679,7 +6018,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:7">
       <c r="A115" t="s">
         <v>119</v>
       </c>
@@ -5702,7 +6041,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
         <v>120</v>
       </c>
@@ -5725,7 +6064,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:7">
       <c r="A117" t="s">
         <v>121</v>
       </c>
@@ -5748,7 +6087,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
         <v>122</v>
       </c>
@@ -5771,7 +6110,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
         <v>123</v>
       </c>
@@ -5794,7 +6133,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
         <v>124</v>
       </c>
@@ -5817,7 +6156,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
         <v>125</v>
       </c>
@@ -5840,7 +6179,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:7">
       <c r="A122" t="s">
         <v>126</v>
       </c>
@@ -5863,7 +6202,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:7">
       <c r="A123" t="s">
         <v>127</v>
       </c>
@@ -5886,7 +6225,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:7">
       <c r="A124" t="s">
         <v>128</v>
       </c>
@@ -5909,7 +6248,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:7">
       <c r="A125" t="s">
         <v>129</v>
       </c>
@@ -5932,7 +6271,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:7">
       <c r="A126" t="s">
         <v>130</v>
       </c>
@@ -5955,7 +6294,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:7">
       <c r="A127" t="s">
         <v>131</v>
       </c>
@@ -5978,7 +6317,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:7">
       <c r="A128" t="s">
         <v>132</v>
       </c>
@@ -6001,7 +6340,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:7">
       <c r="A129" t="s">
         <v>133</v>
       </c>
@@ -6024,7 +6363,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:7">
       <c r="A130" t="s">
         <v>134</v>
       </c>
@@ -6047,7 +6386,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:7">
       <c r="A131" t="s">
         <v>135</v>
       </c>
@@ -6070,7 +6409,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:7">
       <c r="A132" t="s">
         <v>136</v>
       </c>
@@ -6093,7 +6432,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:7">
       <c r="A133" t="s">
         <v>137</v>
       </c>
@@ -6116,7 +6455,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:7">
       <c r="A134" t="s">
         <v>138</v>
       </c>
@@ -6139,7 +6478,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:7">
       <c r="A135" t="s">
         <v>139</v>
       </c>
@@ -6162,7 +6501,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:7">
       <c r="A136" t="s">
         <v>140</v>
       </c>
@@ -6185,7 +6524,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:7">
       <c r="A137" t="s">
         <v>141</v>
       </c>
@@ -6208,7 +6547,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:7">
       <c r="A138" t="s">
         <v>142</v>
       </c>
@@ -6231,7 +6570,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:7">
       <c r="A139" t="s">
         <v>143</v>
       </c>
@@ -6254,7 +6593,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:7">
       <c r="A140" t="s">
         <v>144</v>
       </c>
@@ -6277,7 +6616,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:7">
       <c r="A141" t="s">
         <v>145</v>
       </c>
@@ -6300,7 +6639,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:7">
       <c r="A142" t="s">
         <v>146</v>
       </c>
@@ -6323,7 +6662,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:7">
       <c r="A143" t="s">
         <v>147</v>
       </c>
@@ -6346,7 +6685,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:7">
       <c r="A144" t="s">
         <v>148</v>
       </c>
@@ -6369,7 +6708,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:7">
       <c r="A145" t="s">
         <v>149</v>
       </c>
@@ -6392,7 +6731,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:7">
       <c r="A146" t="s">
         <v>150</v>
       </c>
@@ -6415,7 +6754,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:7">
       <c r="A147" t="s">
         <v>151</v>
       </c>
@@ -6438,7 +6777,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:7">
       <c r="A148" t="s">
         <v>152</v>
       </c>
@@ -6461,7 +6800,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:7">
       <c r="A149" t="s">
         <v>153</v>
       </c>
@@ -6484,7 +6823,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:7">
       <c r="A150" t="s">
         <v>154</v>
       </c>
@@ -6507,7 +6846,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:7">
       <c r="A151" t="s">
         <v>155</v>
       </c>
@@ -6530,7 +6869,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:7">
       <c r="A152" t="s">
         <v>156</v>
       </c>
@@ -6553,7 +6892,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:7">
       <c r="A153" t="s">
         <v>157</v>
       </c>
@@ -6576,7 +6915,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:7">
       <c r="A154" t="s">
         <v>158</v>
       </c>
@@ -6599,7 +6938,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:7">
       <c r="A155" t="s">
         <v>159</v>
       </c>
@@ -6622,7 +6961,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:7">
       <c r="A156" t="s">
         <v>160</v>
       </c>
@@ -6645,7 +6984,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:7">
       <c r="A157" t="s">
         <v>161</v>
       </c>
@@ -6668,7 +7007,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:7">
       <c r="A158" t="s">
         <v>162</v>
       </c>
@@ -6691,7 +7030,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:7">
       <c r="A159" t="s">
         <v>163</v>
       </c>
@@ -6714,7 +7053,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:7">
       <c r="A160" t="s">
         <v>164</v>
       </c>
@@ -6737,7 +7076,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:7">
       <c r="A161" t="s">
         <v>165</v>
       </c>
@@ -6760,7 +7099,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:7">
       <c r="A162" t="s">
         <v>166</v>
       </c>
@@ -6783,7 +7122,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:7">
       <c r="A163" t="s">
         <v>167</v>
       </c>
@@ -6806,7 +7145,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:7">
       <c r="A164" t="s">
         <v>168</v>
       </c>
@@ -6829,7 +7168,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:7">
       <c r="A165" t="s">
         <v>169</v>
       </c>
@@ -6852,7 +7191,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:7">
       <c r="A166" t="s">
         <v>170</v>
       </c>
@@ -6875,7 +7214,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:7">
       <c r="A167" t="s">
         <v>171</v>
       </c>
@@ -6898,7 +7237,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:7">
       <c r="A168" t="s">
         <v>172</v>
       </c>
@@ -6921,7 +7260,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:7">
       <c r="A169" t="s">
         <v>173</v>
       </c>
@@ -6944,7 +7283,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:7">
       <c r="A170" t="s">
         <v>174</v>
       </c>
@@ -6967,7 +7306,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:7">
       <c r="A171" t="s">
         <v>175</v>
       </c>
@@ -6990,7 +7329,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:7">
       <c r="A172" t="s">
         <v>176</v>
       </c>
@@ -7013,7 +7352,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:7">
       <c r="A173" t="s">
         <v>177</v>
       </c>
@@ -7036,7 +7375,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:7">
       <c r="A174" t="s">
         <v>178</v>
       </c>
@@ -7059,7 +7398,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:7">
       <c r="A175" t="s">
         <v>179</v>
       </c>
@@ -7082,7 +7421,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:7">
       <c r="A176" t="s">
         <v>180</v>
       </c>
@@ -7105,7 +7444,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:7">
       <c r="A177" t="s">
         <v>181</v>
       </c>
@@ -7128,7 +7467,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:7">
       <c r="A178" t="s">
         <v>182</v>
       </c>
@@ -7151,7 +7490,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:7">
       <c r="A179" t="s">
         <v>183</v>
       </c>
@@ -7174,7 +7513,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:7">
       <c r="A180" t="s">
         <v>184</v>
       </c>
@@ -7197,7 +7536,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:7">
       <c r="A181" t="s">
         <v>185</v>
       </c>
@@ -7220,7 +7559,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:7">
       <c r="A182" t="s">
         <v>186</v>
       </c>
@@ -7243,7 +7582,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:7">
       <c r="A183" t="s">
         <v>187</v>
       </c>
@@ -7266,7 +7605,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:7">
       <c r="A184" t="s">
         <v>188</v>
       </c>
@@ -7289,7 +7628,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:7">
       <c r="A185" t="s">
         <v>189</v>
       </c>
@@ -7312,7 +7651,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:7">
       <c r="A186" t="s">
         <v>190</v>
       </c>
@@ -7335,7 +7674,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:7">
       <c r="A187" t="s">
         <v>191</v>
       </c>
@@ -7358,7 +7697,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:7">
       <c r="A188" t="s">
         <v>192</v>
       </c>
@@ -7381,7 +7720,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:7">
       <c r="A189" t="s">
         <v>193</v>
       </c>
@@ -7404,7 +7743,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:7">
       <c r="A190" t="s">
         <v>194</v>
       </c>
@@ -7427,7 +7766,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:7">
       <c r="A191" t="s">
         <v>195</v>
       </c>
@@ -7450,7 +7789,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:7">
       <c r="A192" t="s">
         <v>196</v>
       </c>
@@ -7473,7 +7812,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:7">
       <c r="A193" t="s">
         <v>197</v>
       </c>
@@ -7496,7 +7835,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:7">
       <c r="A194" t="s">
         <v>198</v>
       </c>
@@ -7519,7 +7858,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:7">
       <c r="A195" t="s">
         <v>199</v>
       </c>
@@ -7542,7 +7881,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:7">
       <c r="A196" t="s">
         <v>200</v>
       </c>
@@ -7565,7 +7904,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:7">
       <c r="A197" t="s">
         <v>201</v>
       </c>
@@ -7588,7 +7927,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:7">
       <c r="A198" t="s">
         <v>202</v>
       </c>
@@ -7611,7 +7950,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:7">
       <c r="A199" t="s">
         <v>203</v>
       </c>
@@ -7634,7 +7973,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:7">
       <c r="A200" t="s">
         <v>204</v>
       </c>
@@ -7657,7 +7996,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:7">
       <c r="A201" t="s">
         <v>205</v>
       </c>
@@ -7680,7 +8019,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:7">
       <c r="A202" t="s">
         <v>206</v>
       </c>
@@ -7703,7 +8042,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:7">
       <c r="A203" t="s">
         <v>207</v>
       </c>
@@ -7726,7 +8065,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:7">
       <c r="A204" t="s">
         <v>208</v>
       </c>
@@ -7749,7 +8088,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="1:7">
       <c r="A205" t="s">
         <v>209</v>
       </c>
@@ -7772,7 +8111,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:7">
       <c r="A206" t="s">
         <v>210</v>
       </c>
@@ -7795,7 +8134,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:7">
       <c r="A207" t="s">
         <v>211</v>
       </c>
@@ -7818,7 +8157,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="1:7">
       <c r="A208" t="s">
         <v>212</v>
       </c>
@@ -7841,7 +8180,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="1:7">
       <c r="A209" t="s">
         <v>213</v>
       </c>
@@ -7864,7 +8203,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="1:7">
       <c r="A210" t="s">
         <v>214</v>
       </c>
@@ -7887,7 +8226,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="1:7">
       <c r="A211" t="s">
         <v>215</v>
       </c>
@@ -7910,7 +8249,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="1:7">
       <c r="A212" t="s">
         <v>216</v>
       </c>
@@ -7933,7 +8272,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="1:7">
       <c r="A213" t="s">
         <v>217</v>
       </c>
@@ -7956,7 +8295,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="1:7">
       <c r="A214" t="s">
         <v>218</v>
       </c>
@@ -7979,7 +8318,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="1:7">
       <c r="A215" t="s">
         <v>219</v>
       </c>
@@ -8002,7 +8341,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="1:7">
       <c r="A216" t="s">
         <v>220</v>
       </c>
@@ -8025,7 +8364,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="1:7">
       <c r="A217" t="s">
         <v>221</v>
       </c>
@@ -8048,7 +8387,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="1:7">
       <c r="A218" t="s">
         <v>222</v>
       </c>
@@ -8071,7 +8410,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="1:7">
       <c r="A219" t="s">
         <v>223</v>
       </c>
@@ -8094,7 +8433,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" spans="1:7">
       <c r="A220" t="s">
         <v>224</v>
       </c>
@@ -8117,7 +8456,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" spans="1:7">
       <c r="A221" t="s">
         <v>225</v>
       </c>
@@ -8140,7 +8479,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" spans="1:7">
       <c r="A222" t="s">
         <v>226</v>
       </c>
@@ -8163,7 +8502,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" spans="1:7">
       <c r="A223" t="s">
         <v>227</v>
       </c>
@@ -8186,7 +8525,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" spans="1:7">
       <c r="A224" t="s">
         <v>228</v>
       </c>
@@ -8209,7 +8548,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" spans="1:7">
       <c r="A225" t="s">
         <v>229</v>
       </c>
@@ -8232,7 +8571,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" spans="1:7">
       <c r="A226" t="s">
         <v>230</v>
       </c>
@@ -8255,7 +8594,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="1:7">
       <c r="A227" t="s">
         <v>231</v>
       </c>
@@ -8278,7 +8617,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" spans="1:7">
       <c r="A228" t="s">
         <v>232</v>
       </c>
@@ -8301,7 +8640,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" spans="1:7">
       <c r="A229" t="s">
         <v>233</v>
       </c>
@@ -8324,7 +8663,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" spans="1:7">
       <c r="A230" t="s">
         <v>234</v>
       </c>
@@ -8347,7 +8686,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="1:7">
       <c r="A231" t="s">
         <v>235</v>
       </c>
@@ -8370,7 +8709,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="1:7">
       <c r="A232" t="s">
         <v>236</v>
       </c>
@@ -8393,7 +8732,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" spans="1:7">
       <c r="A233" t="s">
         <v>237</v>
       </c>
@@ -8416,7 +8755,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="1:7">
       <c r="A234" t="s">
         <v>238</v>
       </c>
@@ -8439,7 +8778,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" spans="1:7">
       <c r="A235" t="s">
         <v>239</v>
       </c>
@@ -8462,7 +8801,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="1:7">
       <c r="A236" t="s">
         <v>240</v>
       </c>
@@ -8485,7 +8824,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" spans="1:7">
       <c r="A237" t="s">
         <v>241</v>
       </c>
@@ -8508,7 +8847,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" spans="1:7">
       <c r="A238" t="s">
         <v>242</v>
       </c>
@@ -8531,7 +8870,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" spans="1:7">
       <c r="A239" t="s">
         <v>243</v>
       </c>
@@ -8554,7 +8893,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="1:7">
       <c r="A240" t="s">
         <v>244</v>
       </c>
@@ -8577,7 +8916,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="1:7">
       <c r="A241" t="s">
         <v>245</v>
       </c>
@@ -8600,7 +8939,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" spans="1:7">
       <c r="A242" t="s">
         <v>246</v>
       </c>
@@ -8623,7 +8962,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" spans="1:7">
       <c r="A243" t="s">
         <v>247</v>
       </c>
@@ -8646,7 +8985,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" spans="1:7">
       <c r="A244" t="s">
         <v>248</v>
       </c>
@@ -8669,7 +9008,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" spans="1:7">
       <c r="A245" t="s">
         <v>249</v>
       </c>
@@ -8692,7 +9031,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" spans="1:7">
       <c r="A246" t="s">
         <v>250</v>
       </c>
@@ -8715,7 +9054,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" spans="1:7">
       <c r="A247" t="s">
         <v>251</v>
       </c>
@@ -8738,7 +9077,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" spans="1:7">
       <c r="A248" t="s">
         <v>252</v>
       </c>
@@ -8761,7 +9100,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" spans="1:7">
       <c r="A249" t="s">
         <v>253</v>
       </c>
@@ -8784,7 +9123,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" spans="1:7">
       <c r="A250" t="s">
         <v>254</v>
       </c>
@@ -8807,7 +9146,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" spans="1:7">
       <c r="A251" t="s">
         <v>255</v>
       </c>
@@ -8830,7 +9169,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" spans="1:7">
       <c r="A252" t="s">
         <v>256</v>
       </c>
@@ -8853,7 +9192,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" spans="1:7">
       <c r="A253" t="s">
         <v>257</v>
       </c>
@@ -8876,7 +9215,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" spans="1:7">
       <c r="A254" t="s">
         <v>258</v>
       </c>
@@ -8899,7 +9238,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" spans="1:7">
       <c r="A255" t="s">
         <v>259</v>
       </c>
@@ -8922,7 +9261,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" spans="1:7">
       <c r="A256" t="s">
         <v>260</v>
       </c>
@@ -8945,7 +9284,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" spans="1:7">
       <c r="A257" t="s">
         <v>261</v>
       </c>
@@ -8968,7 +9307,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" spans="1:7">
       <c r="A258" t="s">
         <v>262</v>
       </c>
@@ -8991,7 +9330,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" spans="1:7">
       <c r="A259" t="s">
         <v>263</v>
       </c>
@@ -9014,7 +9353,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" spans="1:7">
       <c r="A260" t="s">
         <v>264</v>
       </c>
@@ -9037,7 +9376,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" spans="1:7">
       <c r="A261" t="s">
         <v>265</v>
       </c>
@@ -9060,7 +9399,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" spans="1:7">
       <c r="A262" t="s">
         <v>266</v>
       </c>
@@ -9083,7 +9422,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" spans="1:7">
       <c r="A263" t="s">
         <v>267</v>
       </c>
@@ -9106,7 +9445,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" spans="1:7">
       <c r="A264" t="s">
         <v>268</v>
       </c>
@@ -9129,7 +9468,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" spans="1:7">
       <c r="A265" t="s">
         <v>269</v>
       </c>
@@ -9152,7 +9491,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" spans="1:7">
       <c r="A266" t="s">
         <v>270</v>
       </c>
@@ -9175,7 +9514,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" spans="1:7">
       <c r="A267" t="s">
         <v>271</v>
       </c>
@@ -9198,7 +9537,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" spans="1:7">
       <c r="A268" t="s">
         <v>272</v>
       </c>
@@ -9221,7 +9560,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" spans="1:7">
       <c r="A269" t="s">
         <v>273</v>
       </c>
@@ -9244,7 +9583,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" spans="1:7">
       <c r="A270" t="s">
         <v>274</v>
       </c>
@@ -9267,7 +9606,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" spans="1:7">
       <c r="A271" t="s">
         <v>275</v>
       </c>
@@ -9290,7 +9629,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" spans="1:7">
       <c r="A272" t="s">
         <v>276</v>
       </c>
@@ -9313,7 +9652,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" spans="1:7">
       <c r="A273" t="s">
         <v>277</v>
       </c>
@@ -9336,7 +9675,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" spans="1:7">
       <c r="A274" t="s">
         <v>278</v>
       </c>
@@ -9359,7 +9698,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" spans="1:7">
       <c r="A275" t="s">
         <v>279</v>
       </c>
@@ -9382,7 +9721,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" spans="1:7">
       <c r="A276" t="s">
         <v>280</v>
       </c>
@@ -9405,7 +9744,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" spans="1:7">
       <c r="A277" t="s">
         <v>281</v>
       </c>
@@ -9428,7 +9767,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" spans="1:7">
       <c r="A278" t="s">
         <v>282</v>
       </c>
@@ -9451,7 +9790,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="279">
+    <row r="279" spans="1:7">
       <c r="A279" t="s">
         <v>283</v>
       </c>
@@ -9474,7 +9813,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="280">
+    <row r="280" spans="1:7">
       <c r="A280" t="s">
         <v>284</v>
       </c>
@@ -9497,7 +9836,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="281">
+    <row r="281" spans="1:7">
       <c r="A281" t="s">
         <v>285</v>
       </c>
@@ -9520,7 +9859,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" spans="1:7">
       <c r="A282" t="s">
         <v>286</v>
       </c>
@@ -9543,7 +9882,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="283">
+    <row r="283" spans="1:7">
       <c r="A283" t="s">
         <v>287</v>
       </c>
@@ -9566,7 +9905,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="284">
+    <row r="284" spans="1:7">
       <c r="A284" t="s">
         <v>288</v>
       </c>
@@ -9589,7 +9928,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" spans="1:7">
       <c r="A285" t="s">
         <v>289</v>
       </c>
@@ -9612,7 +9951,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" spans="1:7">
       <c r="A286" t="s">
         <v>290</v>
       </c>
@@ -9635,7 +9974,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" spans="1:7">
       <c r="A287" t="s">
         <v>291</v>
       </c>
@@ -9658,7 +9997,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" spans="1:7">
       <c r="A288" t="s">
         <v>292</v>
       </c>
@@ -9681,7 +10020,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" spans="1:7">
       <c r="A289" t="s">
         <v>293</v>
       </c>
@@ -9704,7 +10043,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" spans="1:7">
       <c r="A290" t="s">
         <v>294</v>
       </c>
@@ -9727,7 +10066,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" spans="1:7">
       <c r="A291" t="s">
         <v>295</v>
       </c>
@@ -9750,7 +10089,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" spans="1:7">
       <c r="A292" t="s">
         <v>296</v>
       </c>
@@ -9773,7 +10112,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" spans="1:7">
       <c r="A293" t="s">
         <v>297</v>
       </c>
@@ -9796,7 +10135,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="294">
+    <row r="294" spans="1:7">
       <c r="A294" t="s">
         <v>298</v>
       </c>
@@ -9819,7 +10158,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" spans="1:7">
       <c r="A295" t="s">
         <v>299</v>
       </c>
@@ -9842,7 +10181,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="296">
+    <row r="296" spans="1:7">
       <c r="A296" t="s">
         <v>300</v>
       </c>
@@ -9865,7 +10204,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="297">
+    <row r="297" spans="1:7">
       <c r="A297" t="s">
         <v>301</v>
       </c>
@@ -9888,7 +10227,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" spans="1:7">
       <c r="A298" t="s">
         <v>302</v>
       </c>
@@ -9911,7 +10250,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" spans="1:7">
       <c r="A299" t="s">
         <v>303</v>
       </c>
@@ -9934,7 +10273,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="300">
+    <row r="300" spans="1:7">
       <c r="A300" t="s">
         <v>304</v>
       </c>
@@ -9957,7 +10296,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="301">
+    <row r="301" spans="1:7">
       <c r="A301" t="s">
         <v>305</v>
       </c>
@@ -9980,7 +10319,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="302">
+    <row r="302" spans="1:7">
       <c r="A302" t="s">
         <v>306</v>
       </c>
@@ -10003,7 +10342,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="303">
+    <row r="303" spans="1:7">
       <c r="A303" t="s">
         <v>307</v>
       </c>
@@ -10026,7 +10365,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="304">
+    <row r="304" spans="1:7">
       <c r="A304" t="s">
         <v>308</v>
       </c>
@@ -10049,7 +10388,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="305">
+    <row r="305" spans="1:7">
       <c r="A305" t="s">
         <v>309</v>
       </c>
@@ -10072,7 +10411,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="306">
+    <row r="306" spans="1:7">
       <c r="A306" t="s">
         <v>310</v>
       </c>
@@ -10095,7 +10434,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="307">
+    <row r="307" spans="1:7">
       <c r="A307" t="s">
         <v>311</v>
       </c>
@@ -10118,7 +10457,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="308">
+    <row r="308" spans="1:7">
       <c r="A308" t="s">
         <v>312</v>
       </c>
@@ -10141,7 +10480,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="309">
+    <row r="309" spans="1:7">
       <c r="A309" t="s">
         <v>313</v>
       </c>
@@ -10164,7 +10503,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="310">
+    <row r="310" spans="1:7">
       <c r="A310" t="s">
         <v>314</v>
       </c>
@@ -10187,7 +10526,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="311">
+    <row r="311" spans="1:7">
       <c r="A311" t="s">
         <v>315</v>
       </c>
@@ -10210,7 +10549,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="312">
+    <row r="312" spans="1:7">
       <c r="A312" t="s">
         <v>316</v>
       </c>
@@ -10233,7 +10572,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="313">
+    <row r="313" spans="1:7">
       <c r="A313" t="s">
         <v>317</v>
       </c>
@@ -10256,7 +10595,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="314">
+    <row r="314" spans="1:7">
       <c r="A314" t="s">
         <v>318</v>
       </c>
@@ -10279,7 +10618,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="315">
+    <row r="315" spans="1:7">
       <c r="A315" t="s">
         <v>319</v>
       </c>
@@ -10302,7 +10641,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="316">
+    <row r="316" spans="1:7">
       <c r="A316" t="s">
         <v>320</v>
       </c>
@@ -10325,7 +10664,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="317">
+    <row r="317" spans="1:7">
       <c r="A317" t="s">
         <v>321</v>
       </c>
@@ -10348,7 +10687,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="318">
+    <row r="318" spans="1:7">
       <c r="A318" t="s">
         <v>322</v>
       </c>
@@ -10371,7 +10710,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="319">
+    <row r="319" spans="1:7">
       <c r="A319" t="s">
         <v>323</v>
       </c>
@@ -10394,7 +10733,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="320">
+    <row r="320" spans="1:7">
       <c r="A320" t="s">
         <v>324</v>
       </c>
@@ -10417,7 +10756,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="321">
+    <row r="321" spans="1:7">
       <c r="A321" t="s">
         <v>325</v>
       </c>
@@ -10440,7 +10779,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="322">
+    <row r="322" spans="1:7">
       <c r="A322" t="s">
         <v>326</v>
       </c>
@@ -10463,7 +10802,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="323">
+    <row r="323" spans="1:7">
       <c r="A323" t="s">
         <v>327</v>
       </c>
@@ -10486,7 +10825,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="324">
+    <row r="324" spans="1:7">
       <c r="A324" t="s">
         <v>328</v>
       </c>
@@ -10509,7 +10848,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="325">
+    <row r="325" spans="1:7">
       <c r="A325" t="s">
         <v>329</v>
       </c>
@@ -10532,7 +10871,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="326">
+    <row r="326" spans="1:7">
       <c r="A326" t="s">
         <v>330</v>
       </c>
@@ -10555,7 +10894,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="327">
+    <row r="327" spans="1:7">
       <c r="A327" t="s">
         <v>331</v>
       </c>
@@ -10578,7 +10917,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="328">
+    <row r="328" spans="1:7">
       <c r="A328" t="s">
         <v>332</v>
       </c>
@@ -10601,7 +10940,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="329">
+    <row r="329" spans="1:7">
       <c r="A329" t="s">
         <v>333</v>
       </c>
@@ -10624,7 +10963,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="330">
+    <row r="330" spans="1:7">
       <c r="A330" t="s">
         <v>334</v>
       </c>
@@ -10647,7 +10986,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="331">
+    <row r="331" spans="1:7">
       <c r="A331" t="s">
         <v>335</v>
       </c>
@@ -10670,7 +11009,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="332">
+    <row r="332" spans="1:7">
       <c r="A332" t="s">
         <v>336</v>
       </c>
@@ -10693,7 +11032,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="333">
+    <row r="333" spans="1:7">
       <c r="A333" t="s">
         <v>337</v>
       </c>
@@ -10716,7 +11055,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="334">
+    <row r="334" spans="1:7">
       <c r="A334" t="s">
         <v>338</v>
       </c>
@@ -10739,7 +11078,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="335">
+    <row r="335" spans="1:7">
       <c r="A335" t="s">
         <v>339</v>
       </c>
@@ -10763,6 +11102,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>